--- a/output/2019/sector_totals_v2.5_year2019.xlsx
+++ b/output/2019/sector_totals_v2.5_year2019.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1627.085679095954</v>
+        <v>1732.368953602848</v>
       </c>
       <c r="C3" t="n">
-        <v>110.2073798366029</v>
+        <v>101.5817106226255</v>
       </c>
       <c r="D3" t="n">
-        <v>647.6553755748266</v>
+        <v>683.9517034150169</v>
       </c>
       <c r="E3" t="n">
-        <v>2046.366164202594</v>
+        <v>1938.873939535928</v>
       </c>
       <c r="F3" t="n">
-        <v>174.3955275745822</v>
+        <v>171.8268513858606</v>
       </c>
       <c r="G3" t="n">
-        <v>82.0885949857993</v>
+        <v>76.0345152075891</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6545.042159324803</v>
+        <v>6650.325433831697</v>
       </c>
       <c r="C16" t="n">
-        <v>939.210524427139</v>
+        <v>930.5848552131617</v>
       </c>
       <c r="D16" t="n">
-        <v>6331.838940972163</v>
+        <v>6368.135268812353</v>
       </c>
       <c r="E16" t="n">
-        <v>9562.150751647296</v>
+        <v>9454.658526980629</v>
       </c>
       <c r="F16" t="n">
-        <v>4588.631023951204</v>
+        <v>4586.062347762482</v>
       </c>
       <c r="G16" t="n">
-        <v>126.9602644310662</v>
+        <v>120.906184652856</v>
       </c>
     </row>
   </sheetData>
